--- a/datasets/commission_formation/data/output/hearings.xlsx
+++ b/datasets/commission_formation/data/output/hearings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>evaluation_letter_url</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>written_questions_url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>video_url</t>
         </is>
@@ -483,17 +488,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>H23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SEJ</t>
+          <t>CHR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Henna Virkkunen</t>
+          <t>Christophe Hansen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -503,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ITRE</t>
+          <t>AGRI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LIBE</t>
+          <t>ENVI, PECH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -516,24 +521,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25031/</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>GLE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stéphane Séjourné</t>
+          <t>Glenn Micallef</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -543,12 +553,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>INTA, ITRE</t>
+          <t>CULT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IMCO</t>
+          <t>EMPL, LIBE, JURI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -556,24 +566,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25030/</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOS</t>
+          <t>DUB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kaja Kallas</t>
+          <t>Maroš Šefčovič</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,12 +598,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AFET</t>
+          <t>INTA, AFCO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>AFET, IMCO, PETI, DEVE, JURI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -596,24 +611,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25029/</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ROS</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Roxana Mînzatu</t>
+          <t>Apostolos Tzitzikostas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -623,12 +643,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EMPL</t>
+          <t>TRAN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CULT</t>
+          <t>ENVI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -636,39 +656,44 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25032/</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DUB</t>
+          <t>EKA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maroš Šefčovič</t>
+          <t>Ekaterina Zaharieva</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>ITRE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AFCO</t>
+          <t>CULT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -676,39 +701,44 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25034/</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Valdis Dombrovskis</t>
+          <t>Magnus Brunner</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LIBE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BUDG</t>
+          <t>DEVE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -716,24 +746,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25038/</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DUP</t>
+          <t>MIC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dubravka Šuica</t>
+          <t>Michael McGrath</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -743,12 +778,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AFET</t>
+          <t>LIBE, IMCO, JURI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DEVE</t>
+          <t>AFCO, CULT, BUDG, CONT, FEMM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -756,24 +791,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25033/</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAD</t>
+          <t>DUP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hadja Lahbib</t>
+          <t>Dubravka Šuica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -783,12 +823,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LIBE, FEMM</t>
+          <t>AFET</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENVI</t>
+          <t>EMPL, LIBE, DROI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -796,24 +836,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25036/</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>H17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WOP</t>
+          <t>JES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wopke Hoekstra</t>
+          <t>Jessika Roswall</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -828,7 +873,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ITRE</t>
+          <t>IMCO, ITRE, AGRI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -836,24 +881,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25037/</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JOZ</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jozef Síkela</t>
+          <t>Dan Jørgensen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -863,12 +913,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DEVE</t>
+          <t>ITRE, EMPL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INTA, BUDG</t>
+          <t>ENVI, REGI, IMCO, ECON</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -876,75 +926,89 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25035/</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>OLI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Marta Kos</t>
+          <t>Olivér Várhelyi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AFET</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>ENVI, AGRI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ITRE, SANT</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25044/</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DAN</t>
+          <t>COS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dan Jørgensen</t>
+          <t>Costas Kadis</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ITRE</t>
+          <t>PECH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENVI, REGI</t>
+          <t>ENVI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -952,24 +1016,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25041/</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H19</t>
+          <t>H26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Apostolos Tzitzikostas</t>
+          <t>Andrius Kubilius</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -979,12 +1048,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TRAN</t>
+          <t>AFET, ITRE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ENVI</t>
+          <t>TRAN, SEDE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -992,24 +1061,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25043/</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H18</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PIO</t>
+          <t>JOZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Piotr Serafin</t>
+          <t>Jozef Síkela</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1019,33 +1093,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BUDG, CONT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>DEVE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AFET, FEMM, INTA, LIBE</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25042/</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H17</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JES</t>
+          <t>HAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jessika Roswall</t>
+          <t>Hadja Lahbib</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1055,12 +1138,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ENVI</t>
+          <t>DEVE, FEMM, LIBE, ENVI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ITRE, IMCO</t>
+          <t>EMPL, SANT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1068,24 +1151,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25039/</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H13</t>
+          <t>H25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OLI</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Olivér Várhelyi</t>
+          <t>Maria Luís Albuquerque</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1095,12 +1183,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ENVI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AGRI</t>
+          <t>IMCO, LIBE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1108,39 +1196,44 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25040/</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COS</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Costas Kadis</t>
+          <t>Marta Kos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PECH</t>
+          <t>AFET</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENVI</t>
+          <t>LIBE, AFCO, DROI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1148,39 +1241,44 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25046/</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H26</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>WOP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Andrius Kubilius</t>
+          <t>Wopke Hoekstra</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFET, ITRE</t>
+          <t>ENVI, ITRE, ECON</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>EMPL, TRAN, FISC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1188,24 +1286,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25045/</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H20</t>
+          <t>H18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIC</t>
+          <t>PIO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Michael McGrath</t>
+          <t>Piotr Serafin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1215,37 +1318,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>BUDG, CONT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>LIBE, JURI</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>AFCO</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25047/</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H21</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Magnus Brunner</t>
+          <t>Valdis Dombrovskis</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1255,48 +1363,57 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LIBE</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>ECON, JURI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BUDG, AFCO, EMPL, IMCO, FISC</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25048/</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H22</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GLE</t>
+          <t>ROS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Glenn Micallef</t>
+          <t>Roxana Mînzatu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CULT</t>
+          <t>EMPL, CULT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EMPL</t>
+          <t>FEMM, LIBE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1304,39 +1421,44 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25051/</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H23</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHR</t>
+          <t>RAF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Christophe Hansen</t>
+          <t>Raffaele Fitto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AGRI</t>
+          <t>REGI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENVI</t>
+          <t>TRAN, BUDG, AGRI, PECH, EMPL, ECON</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1344,39 +1466,44 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25049/</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H24</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EKA</t>
+          <t>KOS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ekaterina Zaharieva</t>
+          <t>Kaja Kallas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ITRE</t>
+          <t>AFET</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BUDG</t>
+          <t>DEVE, INTA, FEMM, SEDE, DROI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1384,60 +1511,74 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25050/</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H25</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Maria Luís Albuquerque</t>
+          <t>Stéphane Séjourné</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>ITRE, IMCO, ENVI, ECON</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>INTA, EMPL, BUDG, JURI</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25052/</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RAF</t>
+          <t>FIT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raffaele Fitto</t>
+          <t>Teresa Ribera</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1447,12 +1588,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>REGI</t>
+          <t>ENVI, ECON, ITRE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BUDG, ECON</t>
+          <t>IMCO, EMPL, TRAN, REGI, AGRI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1460,24 +1601,29 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25053/</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FIT</t>
+          <t>SEJ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Teresa Ribera</t>
+          <t>Henna Virkkunen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1487,12 +1633,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ENVI, ITRE</t>
+          <t>ITRE, IMCO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LIBE, JURI, SEDE, CULT</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1500,9 +1646,14 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241029IPR25054/</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
